--- a/docs/files/rocscience/rs2_60c.xlsx
+++ b/docs/files/rocscience/rs2_60c.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71DBC3B9-A43B-6243-9E0A-99EFD44C8674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E95D610-588A-C249-B900-E3D88174AD4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3480" yWindow="3300" windowWidth="53960" windowHeight="22800" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19900" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="235">
   <si>
     <t>X</t>
   </si>
@@ -450,9 +450,6 @@
     <t>max depth defines the elevation of a horizontal line that is treated as the bottom of the profile</t>
   </si>
   <si>
-    <t>Head:</t>
-  </si>
-  <si>
     <t>seep bc</t>
   </si>
   <si>
@@ -558,40 +555,10 @@
     <t>Distributed Load #6</t>
   </si>
   <si>
-    <t>Specified Head #1</t>
-  </si>
-  <si>
-    <t>Specified Head #2</t>
-  </si>
-  <si>
-    <t>Specified Head #3</t>
-  </si>
-  <si>
-    <t>Specified Head #4</t>
-  </si>
-  <si>
-    <t>Specified Head #5</t>
-  </si>
-  <si>
     <t>Exit Face</t>
   </si>
   <si>
-    <t>Specified Head #1 (2)</t>
-  </si>
-  <si>
     <t>Exit Face (2)</t>
-  </si>
-  <si>
-    <t>Specified Head #2 (2)</t>
-  </si>
-  <si>
-    <t>Specified Head #3 (2)</t>
-  </si>
-  <si>
-    <t>Specified Head #4 (2)</t>
-  </si>
-  <si>
-    <t>Specified Head #5 (2)</t>
   </si>
   <si>
     <t>Distributed Load #1 (2)</t>
@@ -902,6 +869,69 @@
   </si>
   <si>
     <t>nu</t>
+  </si>
+  <si>
+    <t>BC Option:</t>
+  </si>
+  <si>
+    <t>head</t>
+  </si>
+  <si>
+    <t>flux</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #1</t>
+  </si>
+  <si>
+    <t>specified head (len)</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #2</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #3</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #4</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #5</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #1 (2)</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #2 (2)</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #3 (2)</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #4 (2)</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #5 (2)</t>
+  </si>
+  <si>
+    <t>Neumann flux - normal Darcy velocity (len/time), + = inflow</t>
+  </si>
+  <si>
+    <t>polygon</t>
+  </si>
+  <si>
+    <t>Polygons describing the slope geometry</t>
+  </si>
+  <si>
+    <t>piles</t>
+  </si>
+  <si>
+    <t>Piles</t>
+  </si>
+  <si>
+    <t>lloads</t>
+  </si>
+  <si>
+    <t>Line loads</t>
   </si>
 </sst>
 </file>
@@ -1364,19 +1394,22 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1402,9 +1435,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6183,7 +6213,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #1</c:v>
+                  <c:v>Head/Flux BC #1</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6252,7 +6282,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #2</c:v>
+                  <c:v>Head/Flux BC #2</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6321,7 +6351,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #3</c:v>
+                  <c:v>Head/Flux BC #3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6390,7 +6420,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #4</c:v>
+                  <c:v>Head/Flux BC #4</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6462,7 +6492,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #5</c:v>
+                  <c:v>Head/Flux BC #5</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6606,7 +6636,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #1 (2)</c:v>
+                  <c:v>Head/Flux BC #1 (2)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6678,7 +6708,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #2 (2)</c:v>
+                  <c:v>Head/Flux BC #2 (2)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6741,7 +6771,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #3 (2)</c:v>
+                  <c:v>Head/Flux BC #3 (2)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6804,7 +6834,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #4 (2)</c:v>
+                  <c:v>Head/Flux BC #4 (2)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6873,7 +6903,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #5 (2)</c:v>
+                  <c:v>Head/Flux BC #5 (2)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10364,7 +10394,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="32" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19" x14ac:dyDescent="0.25">
@@ -10377,15 +10407,15 @@
         <v>79</v>
       </c>
       <c r="D5" s="34">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
       <c r="F7" s="15" t="s">
         <v>15</v>
       </c>
@@ -10401,10 +10431,10 @@
         <v>9.81</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G8" t="s">
         <v>116</v>
-      </c>
-      <c r="G8" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -10444,71 +10474,92 @@
         <v>0.0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>21</v>
+        <v>229</v>
       </c>
       <c r="G11" t="s">
-        <v>22</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F12" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F13" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F14" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F15" s="1" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="G15" t="s">
-        <v>120</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F16" s="1" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="G16" t="s">
-        <v>37</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>122</v>
+        <v>36</v>
+      </c>
+      <c r="G17" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="F18" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G18" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="G18" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F19" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G19" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F20" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" s="9" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="F20" s="1"/>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F21" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
@@ -10544,36 +10595,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B2" s="58" t="s">
-        <v>142</v>
-      </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="F2" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="J2" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="N2" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="R2" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="V2" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="W2" s="58"/>
-      <c r="X2" s="58"/>
+      <c r="B2" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="F2" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="J2" s="59" t="s">
+        <v>133</v>
+      </c>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="N2" s="59" t="s">
+        <v>134</v>
+      </c>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="R2" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="V2" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -11042,64 +11093,64 @@
         <v>25</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="H2" s="44" t="s">
+        <v>195</v>
+      </c>
+      <c r="I2" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="J2" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="K2" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="L2" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="M2" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="N2" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="O2" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="P2" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q2" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="R2" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="44" t="s">
-        <v>205</v>
-      </c>
-      <c r="H2" s="44" t="s">
-        <v>206</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>190</v>
-      </c>
-      <c r="J2" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="K2" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="L2" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="M2" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="N2" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="O2" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="P2" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q2" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="R2" s="32" t="s">
-        <v>106</v>
-      </c>
       <c r="Z2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="AA2" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="AB2" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
@@ -11130,13 +11181,13 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="Z3" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="AA3" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="AB3" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -11167,7 +11218,7 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="Z4" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -11198,7 +11249,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="Z5" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -11285,13 +11336,13 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="Z8" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="AA8" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="AB8" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
@@ -11322,13 +11373,13 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="Z9" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="AA9" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="AB9" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
@@ -11359,13 +11410,13 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="Z10" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="AA10" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="AB10" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
@@ -11396,13 +11447,13 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="Z11" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="AA11" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="AB11" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -11716,7 +11767,7 @@
     <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="T23" s="46"/>
       <c r="U23" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.2">
@@ -11724,7 +11775,7 @@
       <c r="L24" s="9"/>
       <c r="T24" s="30"/>
       <c r="U24" s="9" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.2">
@@ -11732,7 +11783,7 @@
       <c r="L25" s="9"/>
       <c r="T25" s="33"/>
       <c r="U25" s="9" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -11770,58 +11821,58 @@
         <v>25</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="H2" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="I2" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="J2" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="K2" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="L2" s="45" t="s">
+        <v>159</v>
+      </c>
+      <c r="M2" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="N2" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="O2" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="P2" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="44" t="s">
-        <v>165</v>
-      </c>
-      <c r="H2" s="44" t="s">
-        <v>173</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>190</v>
-      </c>
-      <c r="J2" s="31" t="s">
+      <c r="Q2" s="32" t="s">
         <v>166</v>
-      </c>
-      <c r="K2" s="31" t="s">
-        <v>167</v>
-      </c>
-      <c r="L2" s="45" t="s">
-        <v>170</v>
-      </c>
-      <c r="M2" s="45" t="s">
-        <v>171</v>
-      </c>
-      <c r="N2" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="O2" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="P2" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q2" s="32" t="s">
-        <v>177</v>
       </c>
       <c r="Z2" t="s">
         <v>40</v>
       </c>
       <c r="AA2" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -11848,7 +11899,7 @@
         <v>76</v>
       </c>
       <c r="AA3" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -12051,19 +12102,19 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="S16" s="46"/>
       <c r="T16" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="19:20" x14ac:dyDescent="0.2">
       <c r="S17" s="30"/>
       <c r="T17" s="9" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="19:20" x14ac:dyDescent="0.2">
       <c r="S18" s="33"/>
       <c r="T18" s="9" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -12095,7 +12146,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>3</v>
@@ -12104,10 +12155,10 @@
         <v>4</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -12317,7 +12368,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D036245-91C1-5842-93DD-735018175DE8}">
-  <dimension ref="B2:R24"/>
+  <dimension ref="B2:U24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -12328,57 +12379,60 @@
     <col min="16" max="16" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B2" s="59" t="s">
-        <v>135</v>
-      </c>
-      <c r="C2" s="59"/>
-      <c r="E2" s="55" t="s">
-        <v>130</v>
-      </c>
-      <c r="F2" s="55"/>
-      <c r="H2" s="55" t="s">
-        <v>131</v>
-      </c>
-      <c r="I2" s="55"/>
-      <c r="K2" s="55" t="s">
-        <v>132</v>
-      </c>
-      <c r="L2" s="55"/>
-      <c r="N2" s="55" t="s">
-        <v>133</v>
-      </c>
-      <c r="O2" s="55"/>
-      <c r="Q2" s="55" t="s">
-        <v>134</v>
-      </c>
-      <c r="R2" s="55"/>
-    </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
+    <row r="2" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B2" s="60" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="60"/>
+      <c r="E2" s="56" t="s">
+        <v>217</v>
+      </c>
+      <c r="F2" s="56"/>
+      <c r="H2" s="56" t="s">
+        <v>219</v>
+      </c>
+      <c r="I2" s="56"/>
+      <c r="K2" s="56" t="s">
+        <v>220</v>
+      </c>
+      <c r="L2" s="56"/>
+      <c r="N2" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="O2" s="56"/>
+      <c r="Q2" s="56" t="s">
+        <v>222</v>
+      </c>
+      <c r="R2" s="56"/>
+    </row>
+    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
       <c r="E3" s="36" t="s">
-        <v>94</v>
+        <v>215</v>
       </c>
       <c r="F3" s="37"/>
       <c r="H3" s="36" t="s">
-        <v>94</v>
+        <v>215</v>
       </c>
       <c r="I3" s="37"/>
       <c r="K3" s="36" t="s">
-        <v>94</v>
+        <v>215</v>
       </c>
       <c r="L3" s="37"/>
       <c r="N3" s="36" t="s">
-        <v>94</v>
+        <v>215</v>
       </c>
       <c r="O3" s="37"/>
       <c r="Q3" s="36" t="s">
-        <v>94</v>
+        <v>215</v>
       </c>
       <c r="R3" s="37"/>
-    </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T3" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="28" t="s">
         <v>3</v>
       </c>
@@ -12415,8 +12469,14 @@
       <c r="R4" s="28" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T4" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="U4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" s="3"/>
@@ -12429,8 +12489,14 @@
       <c r="O5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T5" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="U5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="E6" s="3"/>
@@ -12443,8 +12509,10 @@
       <c r="O6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T6" s="1"/>
+      <c r="U6" s="9"/>
+    </row>
+    <row r="7" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="E7" s="3"/>
@@ -12458,7 +12526,7 @@
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="E8" s="3"/>
@@ -12472,7 +12540,7 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="E9" s="3"/>
@@ -12486,7 +12554,7 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="E10" s="3"/>
@@ -12500,7 +12568,7 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="E11" s="3"/>
@@ -12514,7 +12582,7 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="E12" s="3"/>
@@ -12528,7 +12596,7 @@
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="E13" s="3"/>
@@ -12542,7 +12610,7 @@
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="E14" s="3"/>
@@ -12556,7 +12624,7 @@
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="E15" s="3"/>
@@ -12570,7 +12638,7 @@
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="E16" s="3"/>
@@ -12705,13 +12773,18 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3 H3 K3 N3 Q3" xr:uid="{21F200C9-4829-4345-9958-0F754F272AD0}">
+      <formula1>$T$4:$T$5</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C3C734-6227-7445-884D-1F1A5F3909C7}">
-  <dimension ref="B2:R24"/>
+  <dimension ref="B2:U24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -12722,57 +12795,60 @@
     <col min="16" max="16" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B2" s="60" t="s">
-        <v>137</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="E2" s="56" t="s">
-        <v>136</v>
-      </c>
-      <c r="F2" s="56"/>
-      <c r="H2" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="I2" s="56"/>
-      <c r="K2" s="56" t="s">
-        <v>139</v>
-      </c>
-      <c r="L2" s="56"/>
-      <c r="N2" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="O2" s="56"/>
-      <c r="Q2" s="56" t="s">
-        <v>141</v>
-      </c>
-      <c r="R2" s="56"/>
-    </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
+    <row r="2" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B2" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2" s="61"/>
+      <c r="E2" s="57" t="s">
+        <v>223</v>
+      </c>
+      <c r="F2" s="57"/>
+      <c r="H2" s="57" t="s">
+        <v>224</v>
+      </c>
+      <c r="I2" s="57"/>
+      <c r="K2" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="L2" s="57"/>
+      <c r="N2" s="57" t="s">
+        <v>226</v>
+      </c>
+      <c r="O2" s="57"/>
+      <c r="Q2" s="57" t="s">
+        <v>227</v>
+      </c>
+      <c r="R2" s="57"/>
+    </row>
+    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
       <c r="E3" s="38" t="s">
-        <v>94</v>
+        <v>215</v>
       </c>
       <c r="F3" s="39"/>
       <c r="H3" s="38" t="s">
-        <v>94</v>
+        <v>215</v>
       </c>
       <c r="I3" s="39"/>
       <c r="K3" s="38" t="s">
-        <v>94</v>
+        <v>215</v>
       </c>
       <c r="L3" s="39"/>
       <c r="N3" s="38" t="s">
-        <v>94</v>
+        <v>215</v>
       </c>
       <c r="O3" s="39"/>
       <c r="Q3" s="38" t="s">
-        <v>94</v>
+        <v>215</v>
       </c>
       <c r="R3" s="39"/>
-    </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T3" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="28" t="s">
         <v>3</v>
       </c>
@@ -12809,8 +12885,14 @@
       <c r="R4" s="28" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T4" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="U4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" s="3"/>
@@ -12823,8 +12905,14 @@
       <c r="O5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T5" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="U5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="E6" s="3"/>
@@ -12838,7 +12926,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="E7" s="3"/>
@@ -12852,7 +12940,7 @@
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="E8" s="3"/>
@@ -12866,7 +12954,7 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="E9" s="3"/>
@@ -12880,7 +12968,7 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="E10" s="3"/>
@@ -12894,7 +12982,7 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="E11" s="3"/>
@@ -12908,7 +12996,7 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="E12" s="3"/>
@@ -12922,7 +13010,7 @@
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="E13" s="3"/>
@@ -12936,7 +13024,7 @@
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="E14" s="3"/>
@@ -12950,7 +13038,7 @@
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="E15" s="3"/>
@@ -12964,7 +13052,7 @@
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="E16" s="3"/>
@@ -13099,6 +13187,11 @@
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="N2:O2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3 H3 K3 N3 Q3" xr:uid="{68C61D93-1721-F843-8E53-0F0E50006C65}">
+      <formula1>$T$4:$T$5</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13134,11 +13227,11 @@
       <c r="F2"/>
       <c r="G2"/>
       <c r="K2" s="6" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="Y2" s="6"/>
       <c r="AE2" s="6" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.2">
@@ -13158,10 +13251,10 @@
       </c>
       <c r="Y3" s="14"/>
       <c r="AE3" s="1" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="AF3" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.2">
@@ -13181,18 +13274,18 @@
       </c>
       <c r="Y4" s="14"/>
       <c r="AE4" s="1" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="AF4" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D5" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>88</v>
@@ -13202,73 +13295,73 @@
       </c>
       <c r="Y5" s="14"/>
       <c r="AE5" s="1" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="AF5" s="9" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="L6" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="T6" s="1"/>
       <c r="Z6" s="1"/>
       <c r="AA6" s="1"/>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="49"/>
-      <c r="N8" s="49"/>
-      <c r="O8" s="49"/>
-      <c r="P8" s="49"/>
-      <c r="Q8" s="49"/>
-      <c r="R8" s="49"/>
-      <c r="S8" s="49"/>
-      <c r="T8" s="49"/>
-      <c r="U8" s="49"/>
-      <c r="V8" s="49" t="s">
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
+      <c r="L8" s="50"/>
+      <c r="M8" s="50"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="50"/>
+      <c r="P8" s="50"/>
+      <c r="Q8" s="50"/>
+      <c r="R8" s="50"/>
+      <c r="S8" s="50"/>
+      <c r="T8" s="50"/>
+      <c r="U8" s="50"/>
+      <c r="V8" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="W8" s="49"/>
-      <c r="X8" s="49"/>
-      <c r="Y8" s="49"/>
-      <c r="Z8" s="49"/>
-      <c r="AA8" s="49"/>
-      <c r="AB8" s="49" t="s">
+      <c r="W8" s="50"/>
+      <c r="X8" s="50"/>
+      <c r="Y8" s="50"/>
+      <c r="Z8" s="50"/>
+      <c r="AA8" s="50"/>
+      <c r="AB8" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="AC8" s="49"/>
-      <c r="AD8" s="49"/>
-      <c r="AE8" s="49"/>
-      <c r="AF8" s="49"/>
-      <c r="AG8" s="49"/>
-      <c r="AH8" s="49"/>
-      <c r="AI8" s="49"/>
-      <c r="AJ8" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="AK8" s="49"/>
+      <c r="AC8" s="50"/>
+      <c r="AD8" s="50"/>
+      <c r="AE8" s="50"/>
+      <c r="AF8" s="50"/>
+      <c r="AG8" s="50"/>
+      <c r="AH8" s="50"/>
+      <c r="AI8" s="50"/>
+      <c r="AJ8" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK8" s="50"/>
     </row>
     <row r="9" spans="1:37" ht="18" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
@@ -13281,7 +13374,7 @@
         <v>52</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="E9" s="21" t="s">
         <v>66</v>
@@ -13302,37 +13395,37 @@
         <v>80</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="M9" s="21" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="N9" s="21" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="O9" s="21" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="P9" s="21" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="Q9" s="21" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="R9" s="21" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="S9" s="21" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="T9" s="21" t="s">
         <v>85</v>
       </c>
       <c r="U9" s="21" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="V9" s="22" t="s">
         <v>54</v>
@@ -13350,7 +13443,7 @@
         <v>81</v>
       </c>
       <c r="AA9" s="23" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="AB9" s="25" t="s">
         <v>89</v>
@@ -13362,25 +13455,25 @@
         <v>91</v>
       </c>
       <c r="AE9" s="25" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="AF9" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="AG9" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="AG9" s="25" t="s">
-        <v>97</v>
-      </c>
       <c r="AH9" s="25" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="AI9" s="25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ9" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AK9" s="61" t="s">
-        <v>224</v>
+        <v>99</v>
+      </c>
+      <c r="AK9" s="48" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.2">
@@ -13434,7 +13527,7 @@
         <v>0.0</v>
       </c>
       <c r="P10" s="3">
-        <v>4.048</v>
+        <v>4.37</v>
       </c>
       <c r="Q10" s="3">
         <v>70.0</v>
@@ -13498,10 +13591,10 @@
         <v>0.0</v>
       </c>
       <c r="AJ10" s="3">
-        <v>100000.0</v>
+        <v>5500000.0</v>
       </c>
       <c r="AK10" s="3">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.2">
@@ -14724,261 +14817,261 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="inlineStr">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>Profile Line #1</t>
         </is>
       </c>
-      <c r="B4" s="52"/>
-      <c r="D4" s="52" t="s">
+      <c r="B4" s="51"/>
+      <c r="D4" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="G4" s="52" t="s">
+      <c r="E4" s="51"/>
+      <c r="G4" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="52"/>
-      <c r="J4" s="52" t="s">
+      <c r="H4" s="51"/>
+      <c r="J4" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="52"/>
-      <c r="M4" s="52" t="s">
+      <c r="K4" s="51"/>
+      <c r="M4" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="52"/>
-      <c r="P4" s="52" t="s">
+      <c r="N4" s="51"/>
+      <c r="P4" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="52"/>
+      <c r="Q4" s="51"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="52" t="s">
+      <c r="S4" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="52"/>
+      <c r="T4" s="51"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="52" t="s">
+      <c r="V4" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="52"/>
+      <c r="W4" s="51"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="52" t="s">
+      <c r="Y4" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="52"/>
+      <c r="Z4" s="51"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="52" t="s">
+      <c r="AB4" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="52"/>
-      <c r="AE4" s="52" t="s">
+      <c r="AC4" s="51"/>
+      <c r="AE4" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF4" s="51"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="AF4" s="52"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="52" t="s">
+      <c r="AI4" s="51"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="AI4" s="52"/>
-      <c r="AJ4" s="1"/>
-      <c r="AK4" s="52" t="s">
+      <c r="AL4" s="51"/>
+      <c r="AM4" s="1"/>
+      <c r="AN4" s="51" t="s">
         <v>113</v>
       </c>
-      <c r="AL4" s="52"/>
-      <c r="AM4" s="1"/>
-      <c r="AN4" s="52" t="s">
+      <c r="AO4" s="51"/>
+      <c r="AP4" s="1"/>
+      <c r="AQ4" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="AO4" s="52"/>
-      <c r="AP4" s="1"/>
-      <c r="AQ4" s="52" t="s">
-        <v>115</v>
-      </c>
-      <c r="AR4" s="52"/>
+      <c r="AR4" s="51"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B5" s="41">
         <v>1</v>
       </c>
       <c r="D5" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E5" s="41">
         <v>2</v>
       </c>
       <c r="G5" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H5" s="41">
         <v>3</v>
       </c>
       <c r="J5" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K5" s="41">
         <v>4</v>
       </c>
       <c r="M5" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N5" s="41">
         <v>5</v>
       </c>
       <c r="P5" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q5" s="41">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="T5" s="41">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W5" s="41">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Z5" s="41">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AC5" s="41">
         <v>10</v>
       </c>
       <c r="AE5" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AF5" s="41">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AI5" s="41">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AL5" s="41">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AO5" s="41">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AR5" s="41">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="50" t="str">
+      <c r="A6" s="52" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="B6" s="51"/>
-      <c r="D6" s="50" t="str">
+      <c r="B6" s="53"/>
+      <c r="D6" s="52" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="E6" s="51"/>
-      <c r="G6" s="50" t="str">
+      <c r="E6" s="53"/>
+      <c r="G6" s="52" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="H6" s="51"/>
-      <c r="J6" s="50" t="str">
+      <c r="H6" s="53"/>
+      <c r="J6" s="52" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="51"/>
-      <c r="M6" s="50" t="str">
+      <c r="K6" s="53"/>
+      <c r="M6" s="52" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="51"/>
-      <c r="P6" s="50" t="str">
+      <c r="N6" s="53"/>
+      <c r="P6" s="52" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="51"/>
+      <c r="Q6" s="53"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="50" t="str">
+      <c r="S6" s="52" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="51"/>
+      <c r="T6" s="53"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="50" t="str">
+      <c r="V6" s="52" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="51"/>
+      <c r="W6" s="53"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="50" t="str">
+      <c r="Y6" s="52" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="51"/>
+      <c r="Z6" s="53"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="50" t="str">
+      <c r="AB6" s="52" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="51"/>
-      <c r="AE6" s="50" t="str">
+      <c r="AC6" s="53"/>
+      <c r="AE6" s="52" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="51"/>
+      <c r="AF6" s="53"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="50" t="str">
+      <c r="AH6" s="52" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="51"/>
+      <c r="AI6" s="53"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="50" t="str">
+      <c r="AK6" s="52" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="51"/>
+      <c r="AL6" s="53"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="50" t="str">
+      <c r="AN6" s="52" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="51"/>
+      <c r="AO6" s="53"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="50" t="str">
+      <c r="AQ6" s="52" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="51"/>
+      <c r="AR6" s="53"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -15898,36 +15991,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AK6:AL6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AK6:AL6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AQ6:AR6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15961,263 +16054,263 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="51"/>
+      <c r="D4" s="51" t="s">
+        <v>140</v>
+      </c>
+      <c r="E4" s="51"/>
+      <c r="G4" s="51" t="s">
+        <v>141</v>
+      </c>
+      <c r="H4" s="51"/>
+      <c r="J4" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="K4" s="51"/>
+      <c r="M4" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="N4" s="51"/>
+      <c r="P4" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q4" s="51"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="T4" s="51"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="W4" s="51"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="AC4" s="51"/>
+      <c r="AE4" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="AF4" s="51"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="51" t="s">
         <v>150</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="D4" s="52" t="s">
+      <c r="AI4" s="51"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="51" t="s">
         <v>151</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="G4" s="52" t="s">
+      <c r="AL4" s="51"/>
+      <c r="AM4" s="1"/>
+      <c r="AN4" s="51" t="s">
         <v>152</v>
       </c>
-      <c r="H4" s="52"/>
-      <c r="J4" s="52" t="s">
+      <c r="AO4" s="51"/>
+      <c r="AP4" s="1"/>
+      <c r="AQ4" s="51" t="s">
         <v>153</v>
       </c>
-      <c r="K4" s="52"/>
-      <c r="M4" s="52" t="s">
-        <v>154</v>
-      </c>
-      <c r="N4" s="52"/>
-      <c r="P4" s="52" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="52" t="s">
-        <v>156</v>
-      </c>
-      <c r="T4" s="52"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="52" t="s">
-        <v>157</v>
-      </c>
-      <c r="W4" s="52"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="52" t="s">
-        <v>158</v>
-      </c>
-      <c r="Z4" s="52"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="52" t="s">
-        <v>159</v>
-      </c>
-      <c r="AC4" s="52"/>
-      <c r="AE4" s="52" t="s">
-        <v>160</v>
-      </c>
-      <c r="AF4" s="52"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="52" t="s">
-        <v>161</v>
-      </c>
-      <c r="AI4" s="52"/>
-      <c r="AJ4" s="1"/>
-      <c r="AK4" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL4" s="52"/>
-      <c r="AM4" s="1"/>
-      <c r="AN4" s="52" t="s">
-        <v>163</v>
-      </c>
-      <c r="AO4" s="52"/>
-      <c r="AP4" s="1"/>
-      <c r="AQ4" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="AR4" s="52"/>
+      <c r="AR4" s="51"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B5" s="43">
         <v>1</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E5" s="43">
         <v>2</v>
       </c>
       <c r="G5" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H5" s="43">
         <v>3</v>
       </c>
       <c r="J5" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K5" s="43">
         <v>4</v>
       </c>
       <c r="M5" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N5" s="43">
         <v>5</v>
       </c>
       <c r="P5" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q5" s="43">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="T5" s="43">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W5" s="43">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Z5" s="43">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AC5" s="43">
         <v>10</v>
       </c>
       <c r="AE5" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AF5" s="43">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AI5" s="43">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AL5" s="43">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AO5" s="43">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AR5" s="43">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="53" t="str">
+      <c r="A6" s="54" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="B6" s="54"/>
-      <c r="D6" s="53" t="str">
+      <c r="B6" s="55"/>
+      <c r="D6" s="54" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="E6" s="54"/>
-      <c r="G6" s="53" t="str">
+      <c r="E6" s="55"/>
+      <c r="G6" s="54" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="H6" s="54"/>
-      <c r="J6" s="53" t="str">
+      <c r="H6" s="55"/>
+      <c r="J6" s="54" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="54"/>
-      <c r="M6" s="53" t="str">
+      <c r="K6" s="55"/>
+      <c r="M6" s="54" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="54"/>
-      <c r="P6" s="53" t="str">
+      <c r="N6" s="55"/>
+      <c r="P6" s="54" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="54"/>
+      <c r="Q6" s="55"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="53" t="str">
+      <c r="S6" s="54" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="54"/>
+      <c r="T6" s="55"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="53" t="str">
+      <c r="V6" s="54" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="54"/>
+      <c r="W6" s="55"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="53" t="str">
+      <c r="Y6" s="54" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="54"/>
+      <c r="Z6" s="55"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="53" t="str">
+      <c r="AB6" s="54" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="54"/>
-      <c r="AE6" s="53" t="str">
+      <c r="AC6" s="55"/>
+      <c r="AE6" s="54" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="54"/>
+      <c r="AF6" s="55"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="53" t="str">
+      <c r="AH6" s="54" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="54"/>
+      <c r="AI6" s="55"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="53" t="str">
+      <c r="AK6" s="54" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="54"/>
+      <c r="AL6" s="55"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="53" t="str">
+      <c r="AN6" s="54" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="54"/>
+      <c r="AO6" s="55"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="53" t="str">
+      <c r="AQ6" s="54" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="54"/>
+      <c r="AR6" s="55"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -17121,12 +17214,14 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AK6:AL6"/>
     <mergeCell ref="AK4:AL4"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AQ4:AR4"/>
@@ -17143,14 +17238,12 @@
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AQ6:AR6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AK6:AL6"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17166,21 +17259,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="56" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="D2" s="56" t="s">
+      <c r="B2" s="56"/>
+      <c r="D2" s="57" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="56"/>
+      <c r="E2" s="57"/>
       <c r="G2" s="24" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="36" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="B3" s="37" t="inlineStr">
         <is>
@@ -17188,7 +17281,7 @@
         </is>
       </c>
       <c r="D3" s="38" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
@@ -17211,7 +17304,7 @@
         <v>4</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -17224,7 +17317,7 @@
         <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -17233,10 +17326,10 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="G6" s="1" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="H6" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -17762,36 +17855,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="F2" s="58" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="F2" s="57" t="s">
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="J2" s="58" t="s">
         <v>125</v>
       </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="J2" s="57" t="s">
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="N2" s="58" t="s">
         <v>126</v>
       </c>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="N2" s="57" t="s">
+      <c r="O2" s="58"/>
+      <c r="P2" s="58"/>
+      <c r="R2" s="58" t="s">
         <v>127</v>
       </c>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="R2" s="57" t="s">
+      <c r="S2" s="58"/>
+      <c r="T2" s="58"/>
+      <c r="V2" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="V2" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="W2" s="57"/>
-      <c r="X2" s="57"/>
+      <c r="W2" s="58"/>
+      <c r="X2" s="58"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
